--- a/data/exports/insurance_nguong_doi_chieu.xlsx
+++ b/data/exports/insurance_nguong_doi_chieu.xlsx
@@ -16,7 +16,8 @@
     <sheet name="cong_an_toan_von" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ngoai_le" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="universe" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="meta" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="danh_sach_theo_doi" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="meta" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -584,6 +585,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ten</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>loai_hinh</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>san</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>trang_thai</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ly_do</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IFA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bảo hiểm Viễn Đông</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Phi nhân thọ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>OTC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Chưa đủ lịch sử chấm điểm</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Không có dữ liệu EPS chuẩn hóa</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -611,7 +698,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26T17:41:10</t>
+          <t>2026-09-26T21:46:02</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI40"/>
+  <dimension ref="A1:BJ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3403,31 +3490,32 @@
     <col width="22" customWidth="1" min="34" max="34"/>
     <col width="22" customWidth="1" min="35" max="35"/>
     <col width="18" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="40" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="15" customWidth="1" min="41" max="41"/>
-    <col width="17" customWidth="1" min="42" max="42"/>
-    <col width="21" customWidth="1" min="43" max="43"/>
-    <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
-    <col width="22" customWidth="1" min="46" max="46"/>
-    <col width="23" customWidth="1" min="47" max="47"/>
-    <col width="26" customWidth="1" min="48" max="48"/>
-    <col width="23" customWidth="1" min="49" max="49"/>
-    <col width="40" customWidth="1" min="50" max="50"/>
-    <col width="19" customWidth="1" min="51" max="51"/>
-    <col width="21" customWidth="1" min="52" max="52"/>
-    <col width="20" customWidth="1" min="53" max="53"/>
-    <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="27" customWidth="1" min="55" max="55"/>
-    <col width="18" customWidth="1" min="56" max="56"/>
+    <col width="21" customWidth="1" min="37" max="37"/>
+    <col width="40" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="21" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="15" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="43" max="43"/>
+    <col width="21" customWidth="1" min="44" max="44"/>
+    <col width="21" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="23" customWidth="1" min="48" max="48"/>
+    <col width="26" customWidth="1" min="49" max="49"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
+    <col width="40" customWidth="1" min="51" max="51"/>
+    <col width="19" customWidth="1" min="52" max="52"/>
+    <col width="23" customWidth="1" min="53" max="53"/>
+    <col width="20" customWidth="1" min="54" max="54"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="27" customWidth="1" min="56" max="56"/>
     <col width="18" customWidth="1" min="57" max="57"/>
-    <col width="15" customWidth="1" min="58" max="58"/>
-    <col width="28" customWidth="1" min="59" max="59"/>
-    <col width="22" customWidth="1" min="60" max="60"/>
-    <col width="24" customWidth="1" min="61" max="61"/>
+    <col width="18" customWidth="1" min="58" max="58"/>
+    <col width="15" customWidth="1" min="59" max="59"/>
+    <col width="28" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="24" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3613,125 +3701,130 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>gate_status</t>
+          <t>capital_gate_status</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>gate_cap</t>
+          <t>capital_gate_reason</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>gate_reason</t>
+          <t>future_cap_100</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>applied_cap_current</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>prev_period</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>prev_score_50</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>delta_fa_points</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>delta_fa_pct</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>delta_fa_label</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>np_ttm_current</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>historical_ttm_count</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>median_np_ttm_history</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>profit_history_ratio_pct</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>profit_history_status</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>profit_history_note</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>low_eps_base_flag</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>one_off_profit_flag</t>
-        </is>
-      </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>one_off_profit_status</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>data_start_quarter</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>data_end_quarter</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>calculation_version</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>missing_criteria</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>threshold_set</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>threshold_status</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>score_version</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>eps_norm_version</t>
         </is>
@@ -3864,70 +3957,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS2" t="n">
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
         <v>254307973553</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>16</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
         <v>236804722147</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
         <v>107.3914283665064</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY2" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ2" t="b">
         <v>0</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -4060,73 +4160,80 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -15.9%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
         <v>79</v>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -15.9%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
         <v>32898652621</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>16</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>19192985764</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>171.4097693059697</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY3" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ3" t="b">
         <v>0</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -4259,70 +4366,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>VCSH giảm -1.8% YoY</t>
         </is>
       </c>
-      <c r="AS4" t="n">
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
         <v>12752606231</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>8</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>9720596872</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>131.1915965544631</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY4" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ4" t="b">
         <v>0</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
           <t>2023-Q1</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -4455,70 +4569,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS5" t="n">
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
         <v>540431850962</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>16</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>440292899923</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>122.7437124369965</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY5" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ5" t="b">
         <v>0</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -4656,73 +4777,80 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL6" t="n">
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -11.0%</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
         <v>79</v>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -11.0%</t>
-        </is>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
         <v>31604000429</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>16</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>76906171957</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AW6" t="n">
         <v>41.09423161338796</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>BELOW_NORMAL</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Lợi nhuận vẫn thấp đáng kể so với lịch sử</t>
         </is>
       </c>
-      <c r="AY6" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ6" t="b">
         <v>0</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -4855,70 +4983,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS7" t="n">
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
         <v>259786642077</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>16</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>288926812167.5</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>89.91434201904165</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>RECOVERING</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Đang phục hồi về mức bình thường</t>
         </is>
       </c>
-      <c r="AY7" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ7" t="b">
         <v>0</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -5051,70 +5186,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS8" t="n">
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
         <v>2824584416152</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>16</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>1793097627775.5</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>157.5254114666446</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY8" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ8" t="b">
         <v>0</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -5247,70 +5389,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS9" t="n">
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
         <v>324882597229</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>16</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>246738200535</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>131.6709761701108</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY9" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ9" t="b">
         <v>0</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -5443,70 +5592,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS10" t="n">
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
         <v>245548590131</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>16</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>233908440750</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>104.9763699606894</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY10" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ10" t="b">
         <v>0</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -5639,70 +5795,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS11" t="n">
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
         <v>239609896963</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>16</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>183277206657.5</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>130.7363317746172</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY11" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ11" t="b">
         <v>0</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -5835,70 +5998,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS12" t="n">
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
         <v>291456035820</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>16</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>260399577478</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>111.926462647438</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY12" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ12" t="b">
         <v>0</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -6036,73 +6206,80 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL13" t="n">
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -34.7%</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
         <v>79</v>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -34.7%</t>
-        </is>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
         <v>1103154632356</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>16</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>897577164454.5</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>122.9035982690624</v>
       </c>
-      <c r="AW13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY13" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ13" t="b">
         <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="BD13" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
+      <c r="BH13" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH13" t="inlineStr">
+      <c r="BI13" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BJ13" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -6235,70 +6412,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS14" t="n">
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
         <v>437174545748</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>16</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
         <v>368105522441.5</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AW14" t="n">
         <v>118.7633760146797</v>
       </c>
-      <c r="AW14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY14" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ14" t="b">
         <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC14" t="inlineStr">
+      <c r="BD14" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr">
+      <c r="BH14" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH14" t="inlineStr">
+      <c r="BI14" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="BJ14" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -6431,84 +6615,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AL15" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO15" t="n">
+      <c r="AP15" t="n">
         <v>21</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AQ15" t="n">
         <v>-1</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AR15" t="n">
         <v>-4.761904761904767</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AT15" t="n">
         <v>268281653807</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>16</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
         <v>236804722147</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>113.2923580976819</v>
       </c>
-      <c r="AW15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY15" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ15" t="b">
         <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC15" t="inlineStr">
+      <c r="BD15" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr">
+      <c r="BH15" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH15" t="inlineStr">
+      <c r="BI15" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="BJ15" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -6641,92 +6827,94 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL16" t="n">
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -25.3%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
         <v>79</v>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -25.3%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO16" t="n">
+      <c r="AP16" t="n">
         <v>14</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AQ16" t="n">
         <v>-4</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AR16" t="n">
         <v>-28.57142857142857</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AT16" t="n">
         <v>32738142753</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>16</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AV16" t="n">
         <v>22049342819.5</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AW16" t="n">
         <v>148.4767279505811</v>
       </c>
-      <c r="AW16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY16" t="b">
+      <c r="AZ16" t="b">
         <v>1</v>
       </c>
-      <c r="AZ16" t="b">
-        <v>0</v>
-      </c>
       <c r="BA16" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC16" t="inlineStr">
+      <c r="BD16" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BE16" t="inlineStr">
+      <c r="BF16" t="inlineStr">
         <is>
           <t>NEN_SO_SANH_THAP</t>
         </is>
       </c>
-      <c r="BF16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr">
+      <c r="BH16" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH16" t="inlineStr">
+      <c r="BI16" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI16" t="inlineStr">
+      <c r="BJ16" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -6864,89 +7052,91 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO17" t="n">
+      <c r="AP17" t="n">
         <v>10</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AQ17" t="n">
         <v>13</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AR17" t="n">
         <v>130</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AT17" t="n">
         <v>46303045781</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
         <v>9</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
         <v>10106984316</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AW17" t="n">
         <v>458.1291939644086</v>
       </c>
-      <c r="AW17" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY17" t="b">
+      <c r="AZ17" t="b">
         <v>1</v>
       </c>
-      <c r="AZ17" t="b">
-        <v>0</v>
-      </c>
       <c r="BA17" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
           <t>2023-Q1</t>
         </is>
       </c>
-      <c r="BB17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="BD17" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BE17" t="inlineStr">
+      <c r="BF17" t="inlineStr">
         <is>
           <t>NEN_SO_SANH_THAP</t>
         </is>
       </c>
-      <c r="BF17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
+      <c r="BH17" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH17" t="inlineStr">
+      <c r="BI17" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI17" t="inlineStr">
+      <c r="BJ17" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -7079,84 +7269,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO18" t="n">
+      <c r="AP18" t="n">
         <v>19</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AQ18" t="n">
         <v>-8</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AR18" t="n">
         <v>-42.10526315789473</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AT18" t="n">
         <v>473548333049</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AU18" t="n">
         <v>16</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
         <v>453755633267.5</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>104.3619733465285</v>
       </c>
-      <c r="AW18" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY18" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ18" t="b">
         <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="BD18" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
+      <c r="BH18" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH18" t="inlineStr">
+      <c r="BI18" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="BJ18" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -7289,87 +7481,89 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL19" t="n">
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -14.0%</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
         <v>79</v>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -14.0%</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO19" t="n">
+      <c r="AP19" t="n">
         <v>4</v>
       </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ19" t="n">
         <v>0</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
         <v>4946756622</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AU19" t="n">
         <v>16</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
         <v>69091837911.5</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AW19" t="n">
         <v>7.159683070432023</v>
       </c>
-      <c r="AW19" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>BELOW_NORMAL</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>Lợi nhuận vẫn thấp đáng kể so với lịch sử</t>
         </is>
       </c>
-      <c r="AY19" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ19" t="b">
         <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr">
+      <c r="BD19" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr">
+      <c r="BH19" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH19" t="inlineStr">
+      <c r="BI19" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI19" t="inlineStr">
+      <c r="BJ19" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -7502,84 +7696,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AL20" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO20" t="n">
+      <c r="AP20" t="n">
         <v>17</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AQ20" t="n">
         <v>-7</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AR20" t="n">
         <v>-41.17647058823529</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AT20" t="n">
         <v>252283093881</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AU20" t="n">
         <v>16</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AV20" t="n">
         <v>288926812167.5</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AW20" t="n">
         <v>87.31730087228578</v>
       </c>
-      <c r="AW20" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>RECOVERING</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>Đang phục hồi về mức bình thường</t>
         </is>
       </c>
-      <c r="AY20" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ20" t="b">
         <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="BD20" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
+      <c r="BH20" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH20" t="inlineStr">
+      <c r="BI20" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -7712,84 +7908,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AL21" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO21" t="n">
+      <c r="AP21" t="n">
         <v>20</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AQ21" t="n">
         <v>-3</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AR21" t="n">
         <v>-15</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AT21" t="n">
         <v>2951872731110</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AU21" t="n">
         <v>16</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
         <v>1793097627775.5</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AW21" t="n">
         <v>164.6242059207934</v>
       </c>
-      <c r="AW21" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY21" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ21" t="b">
         <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB21" t="inlineStr">
+      <c r="BC21" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC21" t="inlineStr">
+      <c r="BD21" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG21" t="inlineStr">
+      <c r="BH21" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH21" t="inlineStr">
+      <c r="BI21" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI21" t="inlineStr">
+      <c r="BJ21" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -7922,84 +8120,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AL22" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AO22" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO22" t="n">
+      <c r="AP22" t="n">
         <v>17</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AQ22" t="n">
         <v>-3</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AR22" t="n">
         <v>-17.64705882352942</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AT22" t="n">
         <v>326656145273</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AU22" t="n">
         <v>16</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
         <v>258463345787</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AW22" t="n">
         <v>126.3839343557047</v>
       </c>
-      <c r="AW22" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY22" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ22" t="b">
         <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB22" t="inlineStr">
+      <c r="BC22" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC22" t="inlineStr">
+      <c r="BD22" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG22" t="inlineStr">
+      <c r="BH22" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH22" t="inlineStr">
+      <c r="BI22" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI22" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -8132,84 +8332,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AL23" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO23" t="n">
+      <c r="AP23" t="n">
         <v>17</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AQ23" t="n">
         <v>1</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AR23" t="n">
         <v>5.882352941176472</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AT23" t="n">
         <v>251397437942</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AU23" t="n">
         <v>16</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
         <v>233908440750</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AW23" t="n">
         <v>107.4768559595043</v>
       </c>
-      <c r="AW23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY23" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ23" t="b">
         <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB23" t="inlineStr">
+      <c r="BC23" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC23" t="inlineStr">
+      <c r="BD23" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG23" t="inlineStr">
+      <c r="BH23" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH23" t="inlineStr">
+      <c r="BI23" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI23" t="inlineStr">
+      <c r="BJ23" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -8342,84 +8544,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AL24" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO24" t="n">
+      <c r="AP24" t="n">
         <v>22</v>
       </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ24" t="n">
         <v>0</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
         <v>268958802742</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AU24" t="n">
         <v>16</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
         <v>192725344572.5</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AW24" t="n">
         <v>139.5554919559748</v>
       </c>
-      <c r="AW24" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY24" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ24" t="b">
         <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB24" t="inlineStr">
+      <c r="BC24" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC24" t="inlineStr">
+      <c r="BD24" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF24" t="inlineStr">
+      <c r="BG24" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG24" t="inlineStr">
+      <c r="BH24" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH24" t="inlineStr">
+      <c r="BI24" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI24" t="inlineStr">
+      <c r="BJ24" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -8552,84 +8756,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AL25" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO25" t="n">
+      <c r="AP25" t="n">
         <v>13</v>
       </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ25" t="n">
         <v>0</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
         <v>288107463023</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AU25" t="n">
         <v>16</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AV25" t="n">
         <v>262084143217</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AW25" t="n">
         <v>109.9293759197226</v>
       </c>
-      <c r="AW25" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY25" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ25" t="b">
         <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB25" t="inlineStr">
+      <c r="BC25" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC25" t="inlineStr">
+      <c r="BD25" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF25" t="inlineStr">
+      <c r="BG25" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG25" t="inlineStr">
+      <c r="BH25" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH25" t="inlineStr">
+      <c r="BI25" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI25" t="inlineStr">
+      <c r="BJ25" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -8762,87 +8968,89 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL26" t="n">
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -21.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="AM26" t="n">
         <v>79</v>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -21.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AO26" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO26" t="n">
+      <c r="AP26" t="n">
         <v>17</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AQ26" t="n">
         <v>13</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AR26" t="n">
         <v>76.47058823529412</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AT26" t="n">
         <v>1321368200829</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
         <v>16</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
         <v>940884084961.5</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AW26" t="n">
         <v>140.4390000797036</v>
       </c>
-      <c r="AW26" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY26" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ26" t="b">
         <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB26" t="inlineStr">
+      <c r="BC26" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC26" t="inlineStr">
+      <c r="BD26" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF26" t="inlineStr">
+      <c r="BG26" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG26" t="inlineStr">
+      <c r="BH26" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH26" t="inlineStr">
+      <c r="BI26" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI26" t="inlineStr">
+      <c r="BJ26" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -8975,84 +9183,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AL27" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO27" t="n">
+      <c r="AP27" t="n">
         <v>8</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
         <v>12</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AR27" t="n">
         <v>150</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AT27" t="n">
         <v>469624118715</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
         <v>16</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AV27" t="n">
         <v>392531300130.5</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AW27" t="n">
         <v>119.6399162458815</v>
       </c>
-      <c r="AW27" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY27" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ27" t="b">
         <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB27" t="inlineStr">
+      <c r="BC27" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC27" t="inlineStr">
+      <c r="BD27" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF27" t="inlineStr">
+      <c r="BG27" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG27" t="inlineStr">
+      <c r="BH27" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH27" t="inlineStr">
+      <c r="BI27" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI27" t="inlineStr">
+      <c r="BJ27" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -9185,84 +9395,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AO28" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO28" t="n">
+      <c r="AP28" t="n">
         <v>20</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AQ28" t="n">
         <v>4</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AR28" t="n">
         <v>20</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AT28" t="n">
         <v>289974661869</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AU28" t="n">
         <v>16</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
         <v>236804722147</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AW28" t="n">
         <v>122.4530740941027</v>
       </c>
-      <c r="AW28" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AY28" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY28" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ28" t="b">
         <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB28" t="inlineStr">
+      <c r="BC28" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC28" t="inlineStr">
+      <c r="BD28" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF28" t="inlineStr">
+      <c r="BG28" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG28" t="inlineStr">
+      <c r="BH28" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH28" t="inlineStr">
+      <c r="BI28" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI28" t="inlineStr">
+      <c r="BJ28" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -9395,87 +9607,89 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL29" t="n">
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -30.7%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="AM29" t="n">
         <v>79</v>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -30.7%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
+      <c r="AO29" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO29" t="n">
+      <c r="AP29" t="n">
         <v>10</v>
       </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ29" t="n">
         <v>0</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
         <v>17152248871</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AU29" t="n">
         <v>16</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AV29" t="n">
         <v>22049342819.5</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AW29" t="n">
         <v>77.79029520930162</v>
       </c>
-      <c r="AW29" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>RECOVERING</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AY29" t="inlineStr">
         <is>
           <t>Đang phục hồi về mức bình thường</t>
         </is>
       </c>
-      <c r="AY29" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ29" t="b">
         <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB29" t="inlineStr">
+      <c r="BC29" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC29" t="inlineStr">
+      <c r="BD29" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF29" t="inlineStr">
+      <c r="BG29" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG29" t="inlineStr">
+      <c r="BH29" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH29" t="inlineStr">
+      <c r="BI29" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI29" t="inlineStr">
+      <c r="BJ29" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -9608,84 +9822,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AL30" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
+      <c r="AO30" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO30" t="n">
+      <c r="AP30" t="n">
         <v>23</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AQ30" t="n">
         <v>-10</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AR30" t="n">
         <v>-43.47826086956522</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AT30" t="n">
         <v>26387760879</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AU30" t="n">
         <v>10</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
         <v>11429795273.5</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AW30" t="n">
         <v>230.8681848412462</v>
       </c>
-      <c r="AW30" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
+      <c r="AY30" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY30" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ30" t="b">
         <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
           <t>2023-Q1</t>
         </is>
       </c>
-      <c r="BB30" t="inlineStr">
+      <c r="BC30" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC30" t="inlineStr">
+      <c r="BD30" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF30" t="inlineStr">
+      <c r="BG30" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG30" t="inlineStr">
+      <c r="BH30" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH30" t="inlineStr">
+      <c r="BI30" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI30" t="inlineStr">
+      <c r="BJ30" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -9818,84 +10034,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AL31" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
+      <c r="AO31" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO31" t="n">
+      <c r="AP31" t="n">
         <v>11</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AQ31" t="n">
         <v>-4</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AR31" t="n">
         <v>-36.36363636363637</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AT31" t="n">
         <v>429541203431</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AU31" t="n">
         <v>16</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AV31" t="n">
         <v>465583066808</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AW31" t="n">
         <v>92.25876842469806</v>
       </c>
-      <c r="AW31" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>RECOVERING</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
+      <c r="AY31" t="inlineStr">
         <is>
           <t>Đang phục hồi về mức bình thường</t>
         </is>
       </c>
-      <c r="AY31" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ31" t="b">
         <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB31" t="inlineStr">
+      <c r="BC31" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC31" t="inlineStr">
+      <c r="BD31" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF31" t="inlineStr">
+      <c r="BG31" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG31" t="inlineStr">
+      <c r="BH31" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH31" t="inlineStr">
+      <c r="BI31" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI31" t="inlineStr">
+      <c r="BJ31" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -10028,89 +10246,91 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AL32" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO32" t="n">
+      <c r="AP32" t="n">
         <v>4</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AQ32" t="n">
         <v>14</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AR32" t="n">
         <v>350</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AT32" t="n">
         <v>25936883314</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AU32" t="n">
         <v>16</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AV32" t="n">
         <v>65959593505.5</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AW32" t="n">
         <v>39.32238198502128</v>
       </c>
-      <c r="AW32" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>BELOW_NORMAL</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t>Lợi nhuận vẫn thấp đáng kể so với lịch sử</t>
         </is>
       </c>
-      <c r="AY32" t="b">
+      <c r="AZ32" t="b">
         <v>1</v>
       </c>
-      <c r="AZ32" t="b">
-        <v>0</v>
-      </c>
       <c r="BA32" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB32" t="inlineStr">
+      <c r="BC32" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC32" t="inlineStr">
+      <c r="BD32" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BE32" t="inlineStr">
+      <c r="BF32" t="inlineStr">
         <is>
           <t>NEN_SO_SANH_THAP</t>
         </is>
       </c>
-      <c r="BF32" t="inlineStr">
+      <c r="BG32" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG32" t="inlineStr">
+      <c r="BH32" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH32" t="inlineStr">
+      <c r="BI32" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI32" t="inlineStr">
+      <c r="BJ32" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -10243,84 +10463,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AL33" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO33" t="n">
+      <c r="AP33" t="n">
         <v>10</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AQ33" t="n">
         <v>7</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AR33" t="n">
         <v>70</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AT33" t="n">
         <v>298486050380</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AU33" t="n">
         <v>16</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AV33" t="n">
         <v>288926812167.5</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AW33" t="n">
         <v>103.3085327529098</v>
       </c>
-      <c r="AW33" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AY33" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY33" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ33" t="b">
         <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB33" t="inlineStr">
+      <c r="BC33" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC33" t="inlineStr">
+      <c r="BD33" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF33" t="inlineStr">
+      <c r="BG33" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG33" t="inlineStr">
+      <c r="BH33" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH33" t="inlineStr">
+      <c r="BI33" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI33" t="inlineStr">
+      <c r="BJ33" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -10453,84 +10675,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AL34" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
+      <c r="AO34" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO34" t="n">
+      <c r="AP34" t="n">
         <v>17</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AQ34" t="n">
         <v>7</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
         <v>41.1764705882353</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AT34" t="n">
         <v>3319772394221</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AU34" t="n">
         <v>16</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AV34" t="n">
         <v>1793097627775.5</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AW34" t="n">
         <v>185.1417537337038</v>
       </c>
-      <c r="AW34" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY34" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ34" t="b">
         <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB34" t="inlineStr">
+      <c r="BC34" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BD34" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF34" t="inlineStr">
+      <c r="BG34" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG34" t="inlineStr">
+      <c r="BH34" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH34" t="inlineStr">
+      <c r="BI34" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI34" t="inlineStr">
+      <c r="BJ34" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -10663,84 +10887,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AL35" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO35" t="n">
+      <c r="AP35" t="n">
         <v>14</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AQ35" t="n">
         <v>6</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AR35" t="n">
         <v>42.85714285714286</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AT35" t="n">
         <v>334783684523</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
         <v>16</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AV35" t="n">
         <v>264944332556.5</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AW35" t="n">
         <v>126.3600097773771</v>
       </c>
-      <c r="AW35" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AY35" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY35" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ35" t="b">
         <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB35" t="inlineStr">
+      <c r="BC35" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC35" t="inlineStr">
+      <c r="BD35" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF35" t="inlineStr">
+      <c r="BG35" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG35" t="inlineStr">
+      <c r="BH35" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH35" t="inlineStr">
+      <c r="BI35" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI35" t="inlineStr">
+      <c r="BJ35" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -10873,87 +11099,89 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL36" t="n">
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -12.7%</t>
+        </is>
+      </c>
+      <c r="AM36" t="n">
         <v>79</v>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -12.7%</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
+      <c r="AO36" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO36" t="n">
+      <c r="AP36" t="n">
         <v>18</v>
       </c>
-      <c r="AP36" t="n">
+      <c r="AQ36" t="n">
         <v>-7</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AR36" t="n">
         <v>-38.88888888888889</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AT36" t="n">
         <v>259007566381</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AU36" t="n">
         <v>16</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AV36" t="n">
         <v>233908440750</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AW36" t="n">
         <v>110.7303206119978</v>
       </c>
-      <c r="AW36" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AY36" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY36" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ36" t="b">
         <v>0</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB36" t="inlineStr">
+      <c r="BC36" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC36" t="inlineStr">
+      <c r="BD36" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF36" t="inlineStr">
+      <c r="BG36" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG36" t="inlineStr">
+      <c r="BH36" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH36" t="inlineStr">
+      <c r="BI36" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI36" t="inlineStr">
+      <c r="BJ36" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -11086,84 +11314,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
+      <c r="AL37" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
+      <c r="AO37" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO37" t="n">
+      <c r="AP37" t="n">
         <v>22</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AQ37" t="n">
         <v>3</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AR37" t="n">
         <v>13.63636363636365</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AT37" t="n">
         <v>281140587017</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AU37" t="n">
         <v>16</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AV37" t="n">
         <v>197077674917</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AW37" t="n">
         <v>142.6547107050067</v>
       </c>
-      <c r="AW37" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AY37" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY37" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ37" t="b">
         <v>0</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB37" t="inlineStr">
+      <c r="BC37" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC37" t="inlineStr">
+      <c r="BD37" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF37" t="inlineStr">
+      <c r="BG37" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG37" t="inlineStr">
+      <c r="BH37" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH37" t="inlineStr">
+      <c r="BI37" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI37" t="inlineStr">
+      <c r="BJ37" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -11296,84 +11526,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
+      <c r="AL38" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
+      <c r="AO38" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO38" t="n">
+      <c r="AP38" t="n">
         <v>13</v>
       </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ38" t="n">
         <v>0</v>
       </c>
-      <c r="AS38" t="n">
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
         <v>266721530952</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AU38" t="n">
         <v>16</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AV38" t="n">
         <v>275768027968.5</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AW38" t="n">
         <v>96.71952652265644</v>
       </c>
-      <c r="AW38" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>RECOVERING</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>Đang phục hồi về mức bình thường</t>
         </is>
       </c>
-      <c r="AY38" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ38" t="b">
         <v>0</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB38" t="inlineStr">
+      <c r="BC38" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC38" t="inlineStr">
+      <c r="BD38" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF38" t="inlineStr">
+      <c r="BG38" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG38" t="inlineStr">
+      <c r="BH38" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH38" t="inlineStr">
+      <c r="BI38" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI38" t="inlineStr">
+      <c r="BJ38" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -11506,87 +11738,89 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL39" t="n">
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -18.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="AM39" t="n">
         <v>79</v>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -18.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
+      <c r="AO39" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>30</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
         <v>-9</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AR39" t="n">
         <v>-30</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AT39" t="n">
         <v>1324950528035</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
         <v>16</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AV39" t="n">
         <v>970175291660</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AW39" t="n">
         <v>136.5681582931234</v>
       </c>
-      <c r="AW39" t="inlineStr">
+      <c r="AX39" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AY39" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY39" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ39" t="b">
         <v>0</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB39" t="inlineStr">
+      <c r="BC39" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC39" t="inlineStr">
+      <c r="BD39" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF39" t="inlineStr">
+      <c r="BG39" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG39" t="inlineStr">
+      <c r="BH39" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH39" t="inlineStr">
+      <c r="BI39" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI39" t="inlineStr">
+      <c r="BJ39" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -11719,84 +11953,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
+      <c r="AL40" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
+      <c r="AO40" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO40" t="n">
+      <c r="AP40" t="n">
         <v>20</v>
       </c>
-      <c r="AP40" t="n">
+      <c r="AQ40" t="n">
         <v>-9</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AR40" t="n">
         <v>-44.99999999999999</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AT40" t="n">
         <v>462605095991</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
         <v>16</v>
       </c>
-      <c r="AU40" t="n">
+      <c r="AV40" t="n">
         <v>404978985278.5</v>
       </c>
-      <c r="AV40" t="n">
+      <c r="AW40" t="n">
         <v>114.229407650096</v>
       </c>
-      <c r="AW40" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
+      <c r="AY40" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY40" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ40" t="b">
         <v>0</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB40" t="inlineStr">
+      <c r="BC40" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC40" t="inlineStr">
+      <c r="BD40" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF40" t="inlineStr">
+      <c r="BG40" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="BG40" t="inlineStr">
+      <c r="BH40" t="inlineStr">
         <is>
           <t>BAN_DAU_THEO_BANG_SAN_XUAT</t>
         </is>
       </c>
-      <c r="BH40" t="inlineStr">
+      <c r="BI40" t="inlineStr">
         <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI40" t="inlineStr">
+      <c r="BJ40" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -11813,7 +12049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI40"/>
+  <dimension ref="A1:BJ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11852,31 +12088,32 @@
     <col width="22" customWidth="1" min="34" max="34"/>
     <col width="22" customWidth="1" min="35" max="35"/>
     <col width="18" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="40" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="15" customWidth="1" min="41" max="41"/>
-    <col width="17" customWidth="1" min="42" max="42"/>
-    <col width="21" customWidth="1" min="43" max="43"/>
-    <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
-    <col width="22" customWidth="1" min="46" max="46"/>
-    <col width="23" customWidth="1" min="47" max="47"/>
-    <col width="26" customWidth="1" min="48" max="48"/>
-    <col width="23" customWidth="1" min="49" max="49"/>
-    <col width="40" customWidth="1" min="50" max="50"/>
-    <col width="19" customWidth="1" min="51" max="51"/>
-    <col width="21" customWidth="1" min="52" max="52"/>
-    <col width="20" customWidth="1" min="53" max="53"/>
-    <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="27" customWidth="1" min="55" max="55"/>
-    <col width="18" customWidth="1" min="56" max="56"/>
+    <col width="21" customWidth="1" min="37" max="37"/>
+    <col width="40" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="21" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="15" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="43" max="43"/>
+    <col width="21" customWidth="1" min="44" max="44"/>
+    <col width="21" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="23" customWidth="1" min="48" max="48"/>
+    <col width="26" customWidth="1" min="49" max="49"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
+    <col width="40" customWidth="1" min="51" max="51"/>
+    <col width="19" customWidth="1" min="52" max="52"/>
+    <col width="23" customWidth="1" min="53" max="53"/>
+    <col width="20" customWidth="1" min="54" max="54"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="27" customWidth="1" min="56" max="56"/>
     <col width="18" customWidth="1" min="57" max="57"/>
-    <col width="15" customWidth="1" min="58" max="58"/>
-    <col width="21" customWidth="1" min="59" max="59"/>
-    <col width="22" customWidth="1" min="60" max="60"/>
-    <col width="24" customWidth="1" min="61" max="61"/>
+    <col width="18" customWidth="1" min="58" max="58"/>
+    <col width="15" customWidth="1" min="59" max="59"/>
+    <col width="24" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="24" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12062,125 +12299,130 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>gate_status</t>
+          <t>capital_gate_status</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>gate_cap</t>
+          <t>capital_gate_reason</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>gate_reason</t>
+          <t>future_cap_100</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>applied_cap_current</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>prev_period</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>prev_score_50</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>delta_fa_points</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>delta_fa_pct</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>delta_fa_label</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>np_ttm_current</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>historical_ttm_count</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>median_np_ttm_history</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>profit_history_ratio_pct</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>profit_history_status</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>profit_history_note</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>low_eps_base_flag</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>one_off_profit_flag</t>
-        </is>
-      </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>one_off_profit_status</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>data_start_quarter</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>data_end_quarter</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>calculation_version</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>missing_criteria</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>threshold_set</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>threshold_status</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>score_version</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>eps_norm_version</t>
         </is>
@@ -12313,70 +12555,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS2" t="n">
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
         <v>254307973553</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>16</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
         <v>236804722147</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
         <v>107.3914283665064</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY2" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ2" t="b">
         <v>0</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -12509,73 +12758,80 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -15.9%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
         <v>79</v>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -15.9%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
         <v>32898652621</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>16</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>19192985764</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>171.4097693059697</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY3" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ3" t="b">
         <v>0</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -12708,70 +12964,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>VCSH giảm -1.8% YoY</t>
         </is>
       </c>
-      <c r="AS4" t="n">
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
         <v>12752606231</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>8</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>9720596872</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>131.1915965544631</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY4" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ4" t="b">
         <v>0</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
           <t>2023-Q1</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -12904,70 +13167,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS5" t="n">
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
         <v>540431850962</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>16</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>440292899923</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>122.7437124369965</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY5" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ5" t="b">
         <v>0</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -13105,73 +13375,80 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL6" t="n">
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -11.0%</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
         <v>79</v>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -11.0%</t>
-        </is>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
         <v>31604000429</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>16</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>76906171957</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AW6" t="n">
         <v>41.09423161338796</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>BELOW_NORMAL</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Lợi nhuận vẫn thấp đáng kể so với lịch sử</t>
         </is>
       </c>
-      <c r="AY6" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ6" t="b">
         <v>0</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -13304,70 +13581,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS7" t="n">
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
         <v>259786642077</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>16</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>288926812167.5</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>89.91434201904165</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>RECOVERING</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Đang phục hồi về mức bình thường</t>
         </is>
       </c>
-      <c r="AY7" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ7" t="b">
         <v>0</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -13500,70 +13784,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS8" t="n">
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
         <v>2824584416152</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>16</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>1793097627775.5</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>157.5254114666446</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY8" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ8" t="b">
         <v>0</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -13696,70 +13987,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS9" t="n">
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
         <v>324882597229</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>16</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>246738200535</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>131.6709761701108</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY9" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ9" t="b">
         <v>0</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -13892,70 +14190,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS10" t="n">
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
         <v>245548590131</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>16</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>233908440750</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>104.9763699606894</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY10" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ10" t="b">
         <v>0</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -14088,70 +14393,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS11" t="n">
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
         <v>239609896963</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>16</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>183277206657.5</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>130.7363317746172</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY11" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ11" t="b">
         <v>0</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -14284,70 +14596,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS12" t="n">
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
         <v>291456035820</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>16</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>260399577478</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>111.926462647438</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY12" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ12" t="b">
         <v>0</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -14485,73 +14804,80 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL13" t="n">
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -34.7%</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
         <v>79</v>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -34.7%</t>
-        </is>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
         <v>1103154632356</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>16</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>897577164454.5</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>122.9035982690624</v>
       </c>
-      <c r="AW13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY13" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ13" t="b">
         <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="BD13" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BJ13" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -14684,70 +15010,77 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AS14" t="n">
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Chưa có quý so sánh</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
         <v>437174545748</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>16</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
         <v>368105522441.5</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AW14" t="n">
         <v>118.7633760146797</v>
       </c>
-      <c r="AW14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY14" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ14" t="b">
         <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
           <t>2021-Q1</t>
         </is>
       </c>
-      <c r="BB14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="BC14" t="inlineStr">
+      <c r="BD14" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="BJ14" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -14880,84 +15213,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AL15" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO15" t="n">
+      <c r="AP15" t="n">
         <v>30</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AQ15" t="n">
         <v>11</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AR15" t="n">
         <v>36.66666666666667</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AT15" t="n">
         <v>268281653807</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>16</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
         <v>236804722147</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>113.2923580976819</v>
       </c>
-      <c r="AW15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY15" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ15" t="b">
         <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC15" t="inlineStr">
+      <c r="BD15" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="BJ15" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -15090,92 +15425,94 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL16" t="n">
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -25.3%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
         <v>79</v>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -25.3%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO16" t="n">
+      <c r="AP16" t="n">
         <v>13</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AQ16" t="n">
         <v>-3</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AR16" t="n">
         <v>-23.07692307692307</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AT16" t="n">
         <v>32738142753</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>16</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AV16" t="n">
         <v>22049342819.5</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AW16" t="n">
         <v>148.4767279505811</v>
       </c>
-      <c r="AW16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY16" t="b">
+      <c r="AZ16" t="b">
         <v>1</v>
       </c>
-      <c r="AZ16" t="b">
-        <v>0</v>
-      </c>
       <c r="BA16" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC16" t="inlineStr">
+      <c r="BD16" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BE16" t="inlineStr">
+      <c r="BF16" t="inlineStr">
         <is>
           <t>NEN_SO_SANH_THAP</t>
         </is>
       </c>
-      <c r="BF16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI16" t="inlineStr">
+      <c r="BJ16" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -15313,89 +15650,91 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO17" t="n">
+      <c r="AP17" t="n">
         <v>10</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AQ17" t="n">
         <v>13</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AR17" t="n">
         <v>130</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AT17" t="n">
         <v>46303045781</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
         <v>9</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
         <v>10106984316</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AW17" t="n">
         <v>458.1291939644086</v>
       </c>
-      <c r="AW17" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY17" t="b">
+      <c r="AZ17" t="b">
         <v>1</v>
       </c>
-      <c r="AZ17" t="b">
-        <v>0</v>
-      </c>
       <c r="BA17" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
           <t>2023-Q1</t>
         </is>
       </c>
-      <c r="BB17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="BD17" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BE17" t="inlineStr">
+      <c r="BF17" t="inlineStr">
         <is>
           <t>NEN_SO_SANH_THAP</t>
         </is>
       </c>
-      <c r="BF17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI17" t="inlineStr">
+      <c r="BJ17" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -15528,84 +15867,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO18" t="n">
+      <c r="AP18" t="n">
         <v>20</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AQ18" t="n">
         <v>3</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AR18" t="n">
         <v>14.99999999999999</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AT18" t="n">
         <v>473548333049</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AU18" t="n">
         <v>16</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
         <v>453755633267.5</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>104.3619733465285</v>
       </c>
-      <c r="AW18" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY18" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ18" t="b">
         <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="BD18" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="BJ18" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -15738,87 +16079,89 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL19" t="n">
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -14.0%</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
         <v>79</v>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -14.0%</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO19" t="n">
+      <c r="AP19" t="n">
         <v>10</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AQ19" t="n">
         <v>-4</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AR19" t="n">
         <v>-40</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AT19" t="n">
         <v>4946756622</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AU19" t="n">
         <v>16</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
         <v>69091837911.5</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AW19" t="n">
         <v>7.159683070432023</v>
       </c>
-      <c r="AW19" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>BELOW_NORMAL</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>Lợi nhuận vẫn thấp đáng kể so với lịch sử</t>
         </is>
       </c>
-      <c r="AY19" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ19" t="b">
         <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr">
+      <c r="BD19" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI19" t="inlineStr">
+      <c r="BJ19" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -15951,84 +16294,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AL20" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO20" t="n">
+      <c r="AP20" t="n">
         <v>23</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AQ20" t="n">
         <v>-7</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AR20" t="n">
         <v>-30.43478260869566</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AT20" t="n">
         <v>252283093881</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AU20" t="n">
         <v>16</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AV20" t="n">
         <v>288926812167.5</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AW20" t="n">
         <v>87.31730087228578</v>
       </c>
-      <c r="AW20" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>RECOVERING</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>Đang phục hồi về mức bình thường</t>
         </is>
       </c>
-      <c r="AY20" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ20" t="b">
         <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="BD20" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -16161,84 +16506,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AL21" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO21" t="n">
+      <c r="AP21" t="n">
         <v>37</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AQ21" t="n">
         <v>-6</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AR21" t="n">
         <v>-16.21621621621622</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AT21" t="n">
         <v>2951872731110</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AU21" t="n">
         <v>16</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
         <v>1793097627775.5</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AW21" t="n">
         <v>164.6242059207934</v>
       </c>
-      <c r="AW21" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY21" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ21" t="b">
         <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB21" t="inlineStr">
+      <c r="BC21" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC21" t="inlineStr">
+      <c r="BD21" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI21" t="inlineStr">
+      <c r="BJ21" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -16371,84 +16718,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AL22" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AO22" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO22" t="n">
+      <c r="AP22" t="n">
         <v>31</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AQ22" t="n">
         <v>-4</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AR22" t="n">
         <v>-12.90322580645161</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AT22" t="n">
         <v>326656145273</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AU22" t="n">
         <v>16</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
         <v>258463345787</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AW22" t="n">
         <v>126.3839343557047</v>
       </c>
-      <c r="AW22" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY22" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ22" t="b">
         <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB22" t="inlineStr">
+      <c r="BC22" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC22" t="inlineStr">
+      <c r="BD22" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI22" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -16581,84 +16930,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AL23" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO23" t="n">
+      <c r="AP23" t="n">
         <v>34</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AQ23" t="n">
         <v>-1</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AR23" t="n">
         <v>-2.941176470588236</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AT23" t="n">
         <v>251397437942</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AU23" t="n">
         <v>16</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
         <v>233908440750</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AW23" t="n">
         <v>107.4768559595043</v>
       </c>
-      <c r="AW23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY23" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ23" t="b">
         <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB23" t="inlineStr">
+      <c r="BC23" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC23" t="inlineStr">
+      <c r="BD23" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI23" t="inlineStr">
+      <c r="BJ23" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -16791,84 +17142,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AL24" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO24" t="n">
+      <c r="AP24" t="n">
         <v>27</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AQ24" t="n">
         <v>10</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AR24" t="n">
         <v>37.03703703703705</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AT24" t="n">
         <v>268958802742</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AU24" t="n">
         <v>16</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
         <v>192725344572.5</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AW24" t="n">
         <v>139.5554919559748</v>
       </c>
-      <c r="AW24" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY24" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ24" t="b">
         <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB24" t="inlineStr">
+      <c r="BC24" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC24" t="inlineStr">
+      <c r="BD24" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF24" t="inlineStr">
+      <c r="BG24" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG24" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI24" t="inlineStr">
+      <c r="BJ24" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -17001,84 +17354,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AL25" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO25" t="n">
+      <c r="AP25" t="n">
         <v>20</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AQ25" t="n">
         <v>3</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AR25" t="n">
         <v>14.99999999999999</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AT25" t="n">
         <v>288107463023</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AU25" t="n">
         <v>16</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AV25" t="n">
         <v>262084143217</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AW25" t="n">
         <v>109.9293759197226</v>
       </c>
-      <c r="AW25" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AY25" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY25" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ25" t="b">
         <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB25" t="inlineStr">
+      <c r="BC25" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC25" t="inlineStr">
+      <c r="BD25" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF25" t="inlineStr">
+      <c r="BG25" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG25" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI25" t="inlineStr">
+      <c r="BJ25" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -17211,87 +17566,89 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL26" t="n">
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -21.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="AM26" t="n">
         <v>79</v>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -21.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AO26" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO26" t="n">
+      <c r="AP26" t="n">
         <v>24</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AQ26" t="n">
         <v>13</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AR26" t="n">
         <v>54.16666666666667</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AT26" t="n">
         <v>1321368200829</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
         <v>16</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
         <v>940884084961.5</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AW26" t="n">
         <v>140.4390000797036</v>
       </c>
-      <c r="AW26" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY26" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ26" t="b">
         <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB26" t="inlineStr">
+      <c r="BC26" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC26" t="inlineStr">
+      <c r="BD26" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF26" t="inlineStr">
+      <c r="BG26" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG26" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI26" t="inlineStr">
+      <c r="BJ26" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -17424,84 +17781,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AL27" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>2025-Q4</t>
         </is>
       </c>
-      <c r="AO27" t="n">
+      <c r="AP27" t="n">
         <v>13</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
         <v>24</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AR27" t="n">
         <v>184.6153846153846</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AT27" t="n">
         <v>469624118715</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
         <v>16</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AV27" t="n">
         <v>392531300130.5</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AW27" t="n">
         <v>119.6399162458815</v>
       </c>
-      <c r="AW27" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY27" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ27" t="b">
         <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
           <t>2021-Q2</t>
         </is>
       </c>
-      <c r="BB27" t="inlineStr">
+      <c r="BC27" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="BC27" t="inlineStr">
+      <c r="BD27" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF27" t="inlineStr">
+      <c r="BG27" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG27" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI27" t="inlineStr">
+      <c r="BJ27" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -17634,84 +17993,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AO28" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO28" t="n">
+      <c r="AP28" t="n">
         <v>41</v>
       </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ28" t="n">
         <v>0</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
         <v>289974661869</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AU28" t="n">
         <v>16</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
         <v>236804722147</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AW28" t="n">
         <v>122.4530740941027</v>
       </c>
-      <c r="AW28" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AY28" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY28" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ28" t="b">
         <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB28" t="inlineStr">
+      <c r="BC28" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC28" t="inlineStr">
+      <c r="BD28" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF28" t="inlineStr">
+      <c r="BG28" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG28" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI28" t="inlineStr">
+      <c r="BJ28" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -17844,87 +18205,89 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL29" t="n">
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -30.7%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="AM29" t="n">
         <v>79</v>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -30.7%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
+      <c r="AO29" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO29" t="n">
+      <c r="AP29" t="n">
         <v>10</v>
       </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ29" t="n">
         <v>0</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
         <v>17152248871</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AU29" t="n">
         <v>16</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AV29" t="n">
         <v>22049342819.5</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AW29" t="n">
         <v>77.79029520930162</v>
       </c>
-      <c r="AW29" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>RECOVERING</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AY29" t="inlineStr">
         <is>
           <t>Đang phục hồi về mức bình thường</t>
         </is>
       </c>
-      <c r="AY29" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ29" t="b">
         <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB29" t="inlineStr">
+      <c r="BC29" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC29" t="inlineStr">
+      <c r="BD29" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF29" t="inlineStr">
+      <c r="BG29" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG29" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI29" t="inlineStr">
+      <c r="BJ29" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -18057,84 +18420,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AL30" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
+      <c r="AO30" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO30" t="n">
+      <c r="AP30" t="n">
         <v>23</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AQ30" t="n">
         <v>-3</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AR30" t="n">
         <v>-13.04347826086957</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AT30" t="n">
         <v>26387760879</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AU30" t="n">
         <v>10</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
         <v>11429795273.5</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AW30" t="n">
         <v>230.8681848412462</v>
       </c>
-      <c r="AW30" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
+      <c r="AY30" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY30" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ30" t="b">
         <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
           <t>2023-Q1</t>
         </is>
       </c>
-      <c r="BB30" t="inlineStr">
+      <c r="BC30" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC30" t="inlineStr">
+      <c r="BD30" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF30" t="inlineStr">
+      <c r="BG30" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG30" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI30" t="inlineStr">
+      <c r="BJ30" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -18267,84 +18632,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AL31" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
+      <c r="AO31" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO31" t="n">
+      <c r="AP31" t="n">
         <v>23</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AQ31" t="n">
         <v>-6</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AR31" t="n">
         <v>-26.08695652173914</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AT31" t="n">
         <v>429541203431</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AU31" t="n">
         <v>16</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AV31" t="n">
         <v>465583066808</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AW31" t="n">
         <v>92.25876842469806</v>
       </c>
-      <c r="AW31" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>RECOVERING</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
+      <c r="AY31" t="inlineStr">
         <is>
           <t>Đang phục hồi về mức bình thường</t>
         </is>
       </c>
-      <c r="AY31" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ31" t="b">
         <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB31" t="inlineStr">
+      <c r="BC31" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC31" t="inlineStr">
+      <c r="BD31" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF31" t="inlineStr">
+      <c r="BG31" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG31" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI31" t="inlineStr">
+      <c r="BJ31" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -18477,89 +18844,91 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AL32" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO32" t="n">
+      <c r="AP32" t="n">
         <v>6</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AQ32" t="n">
         <v>17</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AR32" t="n">
         <v>283.3333333333334</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AT32" t="n">
         <v>25936883314</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AU32" t="n">
         <v>16</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AV32" t="n">
         <v>65959593505.5</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AW32" t="n">
         <v>39.32238198502128</v>
       </c>
-      <c r="AW32" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>BELOW_NORMAL</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t>Lợi nhuận vẫn thấp đáng kể so với lịch sử</t>
         </is>
       </c>
-      <c r="AY32" t="b">
+      <c r="AZ32" t="b">
         <v>1</v>
       </c>
-      <c r="AZ32" t="b">
-        <v>0</v>
-      </c>
       <c r="BA32" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB32" t="inlineStr">
+      <c r="BC32" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC32" t="inlineStr">
+      <c r="BD32" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BE32" t="inlineStr">
+      <c r="BF32" t="inlineStr">
         <is>
           <t>NEN_SO_SANH_THAP</t>
         </is>
       </c>
-      <c r="BF32" t="inlineStr">
+      <c r="BG32" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG32" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH32" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI32" t="inlineStr">
+      <c r="BJ32" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -18692,84 +19061,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AL33" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO33" t="n">
+      <c r="AP33" t="n">
         <v>16</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AQ33" t="n">
         <v>18</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AR33" t="n">
         <v>112.5</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AT33" t="n">
         <v>298486050380</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AU33" t="n">
         <v>16</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AV33" t="n">
         <v>288926812167.5</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AW33" t="n">
         <v>103.3085327529098</v>
       </c>
-      <c r="AW33" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AY33" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY33" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ33" t="b">
         <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB33" t="inlineStr">
+      <c r="BC33" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC33" t="inlineStr">
+      <c r="BD33" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF33" t="inlineStr">
+      <c r="BG33" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI33" t="inlineStr">
+      <c r="BJ33" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -18902,84 +19273,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AL34" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
+      <c r="AO34" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO34" t="n">
+      <c r="AP34" t="n">
         <v>31</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AQ34" t="n">
         <v>6</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
         <v>19.35483870967742</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AT34" t="n">
         <v>3319772394221</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AU34" t="n">
         <v>16</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AV34" t="n">
         <v>1793097627775.5</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AW34" t="n">
         <v>185.1417537337038</v>
       </c>
-      <c r="AW34" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY34" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ34" t="b">
         <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB34" t="inlineStr">
+      <c r="BC34" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BD34" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF34" t="inlineStr">
+      <c r="BG34" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI34" t="inlineStr">
+      <c r="BJ34" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -19112,84 +19485,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AL35" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO35" t="n">
+      <c r="AP35" t="n">
         <v>27</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AQ35" t="n">
         <v>3</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AR35" t="n">
         <v>11.11111111111112</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AT35" t="n">
         <v>334783684523</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
         <v>16</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AV35" t="n">
         <v>264944332556.5</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AW35" t="n">
         <v>126.3600097773771</v>
       </c>
-      <c r="AW35" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AY35" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY35" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ35" t="b">
         <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB35" t="inlineStr">
+      <c r="BC35" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC35" t="inlineStr">
+      <c r="BD35" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF35" t="inlineStr">
+      <c r="BG35" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG35" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH35" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI35" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI35" t="inlineStr">
+      <c r="BJ35" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -19322,87 +19697,89 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL36" t="n">
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -12.7%</t>
+        </is>
+      </c>
+      <c r="AM36" t="n">
         <v>79</v>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -12.7%</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
+      <c r="AO36" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO36" t="n">
+      <c r="AP36" t="n">
         <v>33</v>
       </c>
-      <c r="AP36" t="n">
+      <c r="AQ36" t="n">
         <v>-6</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AR36" t="n">
         <v>-18.18181818181818</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AT36" t="n">
         <v>259007566381</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AU36" t="n">
         <v>16</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AV36" t="n">
         <v>233908440750</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AW36" t="n">
         <v>110.7303206119978</v>
       </c>
-      <c r="AW36" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AY36" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY36" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ36" t="b">
         <v>0</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB36" t="inlineStr">
+      <c r="BC36" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC36" t="inlineStr">
+      <c r="BD36" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF36" t="inlineStr">
+      <c r="BG36" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG36" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH36" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI36" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI36" t="inlineStr">
+      <c r="BJ36" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -19535,84 +19912,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
+      <c r="AL37" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
+      <c r="AO37" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO37" t="n">
+      <c r="AP37" t="n">
         <v>37</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AQ37" t="n">
         <v>3</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AR37" t="n">
         <v>8.108108108108114</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AT37" t="n">
         <v>281140587017</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AU37" t="n">
         <v>16</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AV37" t="n">
         <v>197077674917</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AW37" t="n">
         <v>142.6547107050067</v>
       </c>
-      <c r="AW37" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AY37" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY37" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ37" t="b">
         <v>0</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB37" t="inlineStr">
+      <c r="BC37" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC37" t="inlineStr">
+      <c r="BD37" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF37" t="inlineStr">
+      <c r="BG37" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG37" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH37" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI37" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI37" t="inlineStr">
+      <c r="BJ37" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -19745,84 +20124,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
+      <c r="AL38" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
+      <c r="AO38" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO38" t="n">
+      <c r="AP38" t="n">
         <v>23</v>
       </c>
-      <c r="AP38" t="n">
+      <c r="AQ38" t="n">
         <v>4</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AR38" t="n">
         <v>17.3913043478261</v>
       </c>
-      <c r="AS38" t="n">
+      <c r="AT38" t="n">
         <v>266721530952</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AU38" t="n">
         <v>16</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AV38" t="n">
         <v>275768027968.5</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AW38" t="n">
         <v>96.71952652265644</v>
       </c>
-      <c r="AW38" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>RECOVERING</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>Đang phục hồi về mức bình thường</t>
         </is>
       </c>
-      <c r="AY38" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ38" t="b">
         <v>0</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB38" t="inlineStr">
+      <c r="BC38" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC38" t="inlineStr">
+      <c r="BD38" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF38" t="inlineStr">
+      <c r="BG38" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG38" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH38" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI38" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI38" t="inlineStr">
+      <c r="BJ38" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -19955,87 +20336,89 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="AL39" t="n">
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -18.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="AM39" t="n">
         <v>79</v>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -18.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
+      <c r="AO39" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>37</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
         <v>-7</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AR39" t="n">
         <v>-18.91891891891892</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AT39" t="n">
         <v>1324950528035</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
         <v>16</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AV39" t="n">
         <v>970175291660</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AW39" t="n">
         <v>136.5681582931234</v>
       </c>
-      <c r="AW39" t="inlineStr">
+      <c r="AX39" t="inlineStr">
         <is>
           <t>NEW_HIGHER_BASE</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AY39" t="inlineStr">
         <is>
           <t>Đã vượt rõ mặt bằng lợi nhuận lịch sử</t>
         </is>
       </c>
-      <c r="AY39" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ39" t="b">
         <v>0</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB39" t="inlineStr">
+      <c r="BC39" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC39" t="inlineStr">
+      <c r="BD39" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF39" t="inlineStr">
+      <c r="BG39" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG39" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH39" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI39" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI39" t="inlineStr">
+      <c r="BJ39" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -20168,84 +20551,86 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
+      <c r="AL40" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
+      <c r="AO40" t="inlineStr">
         <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="AO40" t="n">
+      <c r="AP40" t="n">
         <v>37</v>
       </c>
-      <c r="AP40" t="n">
+      <c r="AQ40" t="n">
         <v>-14</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AR40" t="n">
         <v>-37.83783783783784</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AT40" t="n">
         <v>462605095991</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
         <v>16</v>
       </c>
-      <c r="AU40" t="n">
+      <c r="AV40" t="n">
         <v>404978985278.5</v>
       </c>
-      <c r="AV40" t="n">
+      <c r="AW40" t="n">
         <v>114.229407650096</v>
       </c>
-      <c r="AW40" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>NORMAL_RANGE</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
+      <c r="AY40" t="inlineStr">
         <is>
           <t>Đã trở lại hoặc nhỉnh hơn nền lịch sử</t>
         </is>
       </c>
-      <c r="AY40" t="b">
-        <v>0</v>
-      </c>
       <c r="AZ40" t="b">
         <v>0</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
+          <t>NOT_EVALUATED</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
           <t>2021-Q3</t>
         </is>
       </c>
-      <c r="BB40" t="inlineStr">
+      <c r="BC40" t="inlineStr">
         <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="BC40" t="inlineStr">
+      <c r="BD40" t="inlineStr">
         <is>
           <t>PROFIT_HISTORY_CONTEXT_V1</t>
         </is>
       </c>
-      <c r="BF40" t="inlineStr">
+      <c r="BG40" t="inlineStr">
         <is>
           <t>ba_v2</t>
         </is>
       </c>
-      <c r="BG40" t="inlineStr">
-        <is>
-          <t>DE_XUAT_CHO_BA_KHOA</t>
-        </is>
-      </c>
       <c r="BH40" t="inlineStr">
         <is>
+          <t>DA_KHOA_V1_DE_VAN_HANH</t>
+        </is>
+      </c>
+      <c r="BI40" t="inlineStr">
+        <is>
           <t>INS_TOAN_NGANH_50_V1</t>
         </is>
       </c>
-      <c r="BI40" t="inlineStr">
+      <c r="BJ40" t="inlineStr">
         <is>
           <t>EPS_STD_IAS33_DEDUP_V2</t>
         </is>
@@ -20262,7 +20647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -20274,9 +20659,10 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20327,17 +20713,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>gate_status</t>
+          <t>capital_gate_status</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>gate_cap</t>
+          <t>capital_gate_reason</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>gate_reason</t>
+          <t>future_cap_100</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>applied_cap_current</t>
         </is>
       </c>
     </row>
@@ -20378,7 +20769,7 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
@@ -20421,13 +20812,13 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -30.7%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>79</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -30.7%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -20467,7 +20858,7 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
@@ -20510,7 +20901,7 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
@@ -20553,7 +20944,7 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
@@ -20596,7 +20987,7 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
@@ -20639,7 +21030,7 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
@@ -20682,7 +21073,7 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
@@ -20725,13 +21116,13 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -12.7%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>79</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -12.7%</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -20771,7 +21162,7 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
@@ -20814,7 +21205,7 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
@@ -20857,13 +21248,13 @@
           <t>Cảnh báo</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>đệm vốn giảm -18.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>79</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>đệm vốn giảm -18.1%; khoảng cách tăng trưởng &gt; 20 đpt hai quý liên tiếp</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -20903,7 +21294,7 @@
           <t>Đạt</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>chưa phát hiện cảnh báo vốn từ BCTC</t>
         </is>
@@ -21028,7 +21419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -21037,6 +21428,9 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21070,6 +21464,21 @@
           <t>insurance_type</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ranked</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>watchlist_status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>watchlist_reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21102,6 +21511,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21134,6 +21546,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21166,6 +21581,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21198,6 +21616,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21230,6 +21651,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21262,6 +21686,9 @@
           <t>Phi nhân thọ</t>
         </is>
       </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21294,11 +21721,14 @@
           <t>Holding/Hỗn hợp</t>
         </is>
       </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MIG</t>
+          <t>IFA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -21308,12 +21738,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bảo hiểm Quân đội</t>
+          <t>Bảo hiểm Viễn Đông</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HOSE</t>
+          <t>OTC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -21324,13 +21754,26 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Phi nhân thọ</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Chưa đủ lịch sử chấm điểm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Không có dữ liệu EPS chuẩn hóa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PGI</t>
+          <t>MIG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -21340,7 +21783,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bảo hiểm PJICO</t>
+          <t>Bảo hiểm Quân đội</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -21357,12 +21800,15 @@
         <is>
           <t>Phi nhân thọ</t>
         </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PRE</t>
+          <t>PGI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -21372,29 +21818,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tái bảo hiểm PVI</t>
+          <t>Bảo hiểm PJICO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HNX</t>
+          <t>HOSE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tái bảo hiểm</t>
-        </is>
+          <t>Phi nhân thọ</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>PRE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -21404,7 +21853,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bảo hiểm Bưu điện</t>
+          <t>Tái bảo hiểm PVI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -21414,19 +21863,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Phi nhân thọ</t>
-        </is>
+          <t>Tái bảo hiểm</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PVI</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -21436,7 +21888,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PVI Holdings</t>
+          <t>Bảo hiểm Bưu điện</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21451,40 +21903,81 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Holding/Hỗn hợp</t>
-        </is>
+          <t>Phi nhân thọ</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BH</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PVI Holdings</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HNX</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8536</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Holding/Hỗn hợp</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>VNR</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>BH</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Tái bảo hiểm Quốc gia</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>HNX</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>8538</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Tái bảo hiểm</t>
         </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
